--- a/ecuacion-util-excel-report-to-pdf-sample/test-data/invoice-2.xlsx
+++ b/ecuacion-util-excel-report-to-pdf-sample/test-data/invoice-2.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" checkCompatibility="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20FE27D-379B-784C-BBE6-DDBB0EF0839F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3973DA6-5770-934D-8C0D-68A79955379E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="520" windowWidth="28800" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="invoice" sheetId="24" r:id="rId1"/>
@@ -178,11 +178,11 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="48">
     <font>
       <sz val="11"/>
-      <name val="Meiryo UI"/>
-      <family val="2"/>
+      <name val="Yu Gothic"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -385,110 +385,89 @@
       <b/>
       <sz val="20"/>
       <color theme="4" tint="-0.499984740745262"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <sz val="16"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <b/>
       <sz val="36"/>
       <color theme="4" tint="-0.249977111117893"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
+      <name val="Yu Gothic Regular"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Yu Gothic Regular"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="4" tint="-0.499984740745262"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Yu Gothic Regular"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="4" tint="-0.249977111117893"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Yu Gothic Regular"/>
     </font>
   </fonts>
   <fills count="25">
@@ -979,143 +958,143 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="36" fillId="23" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="36" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="10" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="36" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="40" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="42" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="42" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="44" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="22" fillId="23" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="40" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1125,16 +1104,16 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1651,17 +1630,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="13" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="13" customWidth="1"/>
-    <col min="4" max="6" width="6.7109375" style="13" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="13" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" style="13" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="13" customWidth="1"/>
-    <col min="10" max="10" width="29.140625" style="13" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="6.83203125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" style="13" customWidth="1"/>
+    <col min="4" max="6" width="6.83203125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="29.33203125" style="13" customWidth="1"/>
+    <col min="11" max="16384" width="9.33203125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="46.5" customHeight="1">
@@ -1715,10 +1694,10 @@
         <v>7</v>
       </c>
       <c r="G4" s="58"/>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="22"/>
     </row>
     <row r="5" spans="1:11" ht="19.5" customHeight="1">
       <c r="A5" s="16"/>
@@ -1730,10 +1709,10 @@
         <v>2034</v>
       </c>
       <c r="G5" s="59"/>
-      <c r="H5" s="22">
+      <c r="H5" s="23">
         <v>43152</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="17"/>
@@ -1744,7 +1723,7 @@
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
-      <c r="J6" s="23"/>
+      <c r="J6" s="24"/>
     </row>
     <row r="7" spans="1:11" ht="20" customHeight="1">
       <c r="A7" s="61" t="s">
@@ -1753,15 +1732,15 @@
       <c r="B7" s="61"/>
       <c r="C7" s="61"/>
       <c r="D7" s="17"/>
-      <c r="E7" s="23"/>
+      <c r="E7" s="24"/>
       <c r="F7" s="58" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="58"/>
-      <c r="H7" s="52" t="s">
+      <c r="H7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="22" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1772,15 +1751,15 @@
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
-      <c r="E8" s="23"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="60">
         <v>564</v>
       </c>
       <c r="G8" s="60"/>
-      <c r="H8" s="53" t="s">
+      <c r="H8" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="22"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1">
       <c r="A9" s="17" t="s">
@@ -1789,11 +1768,11 @@
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
-      <c r="E9" s="23"/>
+      <c r="E9" s="24"/>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
-      <c r="J9" s="23"/>
+      <c r="J9" s="24"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="17" t="s">
@@ -1802,11 +1781,11 @@
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
-      <c r="E10" s="23"/>
+      <c r="E10" s="24"/>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
-      <c r="J10" s="23"/>
+      <c r="J10" s="24"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
       <c r="A11" s="17" t="s">
@@ -1815,11 +1794,11 @@
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
-      <c r="E11" s="23"/>
+      <c r="E11" s="24"/>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="27" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1830,11 +1809,11 @@
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
-      <c r="E12" s="23"/>
+      <c r="E12" s="24"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="22" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1849,7 +1828,7 @@
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="22" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1862,258 +1841,258 @@
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="22" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="20" customHeight="1">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="52" t="s">
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="52" t="s">
+      <c r="G15" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="26"/>
+      <c r="J15" s="29"/>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="29">
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32">
         <v>1</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="33">
         <v>200</v>
       </c>
-      <c r="H16" s="46">
+      <c r="H16" s="34">
         <f>IF(F16="",ROUND(1*G16,2),ROUND(F16*G16,2))</f>
         <v>200</v>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="22"/>
     </row>
     <row r="17" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="32">
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="37">
         <v>5</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="38">
         <v>75</v>
       </c>
-      <c r="H17" s="48">
+      <c r="H17" s="39">
         <f t="shared" ref="H17:H30" si="0">IF(F17="",ROUND(1*G17,2),ROUND(F17*G17,2))</f>
         <v>375</v>
       </c>
-      <c r="J17" s="21"/>
+      <c r="J17" s="22"/>
     </row>
     <row r="18" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="47">
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="38">
         <v>-50</v>
       </c>
-      <c r="H18" s="48">
+      <c r="H18" s="39">
         <f t="shared" si="0"/>
         <v>-50</v>
       </c>
-      <c r="J18" s="21" t="s">
+      <c r="J18" s="22" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="48">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="26"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="48">
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="26"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="48">
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="26"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="48">
+      <c r="A22" s="35"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="26"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="48">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="26"/>
+      <c r="J23" s="29"/>
     </row>
     <row r="24" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="48">
+      <c r="A24" s="35"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="26"/>
+      <c r="J24" s="29"/>
     </row>
     <row r="25" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="48">
+      <c r="A25" s="35"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="39">
         <f t="shared" ref="H25" si="1">IF(F25="",ROUND(1*G25,2),ROUND(F25*G25,2))</f>
         <v>0</v>
       </c>
-      <c r="J25" s="26"/>
+      <c r="J25" s="29"/>
     </row>
     <row r="26" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48">
+      <c r="A26" s="35"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="26"/>
+      <c r="J26" s="29"/>
     </row>
     <row r="27" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="48">
+      <c r="A27" s="35"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="26"/>
+      <c r="J27" s="29"/>
     </row>
     <row r="28" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="48">
+      <c r="A28" s="35"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="26"/>
+      <c r="J28" s="29"/>
     </row>
     <row r="29" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A29" s="30"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="48">
+      <c r="A29" s="35"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J29" s="26"/>
+      <c r="J29" s="29"/>
     </row>
     <row r="30" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="50">
+      <c r="A30" s="41"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J30" s="26"/>
-    </row>
-    <row r="31" spans="1:10" s="37" customFormat="1" ht="20.25" customHeight="1">
+      <c r="J30" s="29"/>
+    </row>
+    <row r="31" spans="1:10" s="48" customFormat="1" ht="20.25" customHeight="1">
       <c r="A31" s="62" t="s">
         <v>28</v>
       </c>
@@ -2125,86 +2104,86 @@
         <v>29</v>
       </c>
       <c r="G31" s="63"/>
-      <c r="H31" s="51">
+      <c r="H31" s="47">
         <f>SUM(H16:H30)</f>
         <v>525</v>
       </c>
-      <c r="J31" s="21"/>
+      <c r="J31" s="22"/>
     </row>
     <row r="32" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A32" s="38"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="63" t="s">
         <v>30</v>
       </c>
       <c r="G32" s="63"/>
-      <c r="H32" s="40">
+      <c r="H32" s="51">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="J32" s="21" t="s">
+      <c r="J32" s="22" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A33" s="38"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="55" t="s">
+      <c r="A33" s="49"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="G33" s="55"/>
-      <c r="H33" s="51">
+      <c r="G33" s="46"/>
+      <c r="H33" s="47">
         <f>H31*H32</f>
         <v>22.3125</v>
       </c>
-      <c r="J33" s="21"/>
+      <c r="J33" s="22"/>
     </row>
     <row r="34" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A34" s="38"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="41" t="s">
+      <c r="A34" s="49"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="G34" s="41"/>
-      <c r="H34" s="42">
+      <c r="G34" s="52"/>
+      <c r="H34" s="53">
         <f>H31+H33</f>
         <v>547.3125</v>
       </c>
-      <c r="J34" s="21" t="s">
+      <c r="J34" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="18">
       <c r="A35" s="16"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="J35" s="21" t="s">
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="J35" s="22" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="J36" s="21"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="J36" s="22"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1">
       <c r="A37" s="64" t="s">
@@ -2217,7 +2196,7 @@
       <c r="F37" s="64"/>
       <c r="G37" s="64"/>
       <c r="H37" s="64"/>
-      <c r="J37" s="26"/>
+      <c r="J37" s="29"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1">
       <c r="A38" s="57" t="s">
@@ -2230,12 +2209,12 @@
       <c r="F38" s="57"/>
       <c r="G38" s="57"/>
       <c r="H38" s="57"/>
-      <c r="J38" s="21" t="s">
+      <c r="J38" s="22" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="J39" s="44"/>
+      <c r="J39" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2263,7 +2242,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.25"/>
-  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" scale="97" fitToHeight="0" orientation="portrait" r:id="rId3"/>
   <drawing r:id="rId4"/>
 </worksheet>
 </file>
@@ -2274,10 +2253,10 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="78.7109375" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="78.83203125" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="46.5" customHeight="1"/>
@@ -2307,7 +2286,7 @@
     <row r="7" spans="1:2" ht="16">
       <c r="A7" s="10"/>
     </row>
-    <row r="8" spans="1:2" ht="68">
+    <row r="8" spans="1:2" ht="85">
       <c r="A8" s="10" t="s">
         <v>41</v>
       </c>
